--- a/LinkedIN-Posts.xlsx
+++ b/LinkedIN-Posts.xlsx
@@ -24,14 +24,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Days</t>
   </si>
   <si>
-    <t>Post Link</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/posts/venkatesh-gangavarapu_100daysofcloud-aws-autoscaling-share-7485024154300190721-h8Bw/</t>
   </si>
   <si>
@@ -177,6 +174,12 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/venkatesh-gangavarapu_100daysofcloud-aws-nat-share-7486711187976581120-oVAQ/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/venkatesh-gangavarapu_100daysofcloud-aws-ebs-share-7487082403384176640-K2Gy/</t>
+  </si>
+  <si>
+    <t>LinkedIN Posts</t>
   </si>
 </sst>
 </file>
@@ -516,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,7 +527,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -532,7 +535,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -540,7 +543,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -548,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -556,7 +559,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -564,7 +567,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,7 +575,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -580,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -588,7 +591,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -596,7 +599,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -604,7 +607,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -612,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -620,7 +623,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -628,7 +631,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -636,7 +639,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -644,7 +647,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -652,7 +655,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -660,7 +663,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -668,7 +671,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -676,7 +679,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -684,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -692,7 +695,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -700,7 +703,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -708,7 +711,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -716,7 +719,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -724,7 +727,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -732,7 +735,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -740,7 +743,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -748,7 +751,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -756,7 +759,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -764,7 +767,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -772,7 +775,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -780,7 +783,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -788,7 +791,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -796,7 +799,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -804,7 +807,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -812,7 +815,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -820,7 +823,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -828,7 +831,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -836,7 +839,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -844,7 +847,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -852,7 +855,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -860,7 +863,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -868,7 +871,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -876,7 +879,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -884,7 +887,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -892,7 +895,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -900,7 +903,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -908,11 +911,14 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -967,6 +973,7 @@
     <hyperlink ref="B27" r:id="rId47"/>
     <hyperlink ref="B30" r:id="rId48"/>
     <hyperlink ref="B31" r:id="rId49"/>
+    <hyperlink ref="B51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
